--- a/tmp/P H Medical_Daily_Service_Report.xlsx
+++ b/tmp/P H Medical_Daily_Service_Report.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="24">
   <si>
     <r>
       <t xml:space="preserve">                                                                   </t>
@@ -74,43 +74,31 @@
     <t>Image 2</t>
   </si>
   <si>
-    <t>Regular</t>
-  </si>
-  <si>
-    <t>18:18:20</t>
-  </si>
-  <si>
-    <t>Gr, Reception, Backside Of Visitor Table</t>
-  </si>
-  <si>
-    <t>Twice A Week</t>
+    <t>Complaint</t>
+  </si>
+  <si>
+    <t>10:58:20</t>
+  </si>
+  <si>
+    <t>3rd, Reception, Backside Of Visitor Table</t>
   </si>
   <si>
     <t>termiproof</t>
   </si>
   <si>
-    <t>["By drilling","Injecting process"]</t>
-  </si>
-  <si>
     <t>NA</t>
   </si>
   <si>
-    <t>Pest_emp1</t>
+    <t>Open</t>
+  </si>
+  <si>
+    <t>near balcony</t>
+  </si>
+  <si>
+    <t>Ph_admin</t>
   </si>
   <si>
     <t>No Image</t>
-  </si>
-  <si>
-    <t>18:21:48</t>
-  </si>
-  <si>
-    <t>Daily</t>
-  </si>
-  <si>
-    <t>Termiproof Baiting</t>
-  </si>
-  <si>
-    <t>["Placement of Baits"]</t>
   </si>
 </sst>
 </file>
@@ -763,7 +751,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>15</v>
       </c>
@@ -782,52 +770,21 @@
       <c r="F4" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="G4" s="3"/>
+      <c r="G4" s="3" t="s">
+        <v>21</v>
+      </c>
       <c r="H4" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="K4" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="G5" s="3"/>
-      <c r="H5" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="J5" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="K5" s="1" t="s">
-        <v>23</v>
-      </c>
+    <row r="5" spans="8:8" x14ac:dyDescent="0.25">
+      <c r="H5" s="3"/>
     </row>
     <row r="6" spans="8:8" x14ac:dyDescent="0.25">
       <c r="H6" s="3"/>
